--- a/output/full_scan/batch_seq2_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq2_2026-06-12.xlsx
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>229.983804622141</v>
+        <v>229.9838046221409</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>44.05</v>
